--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.69088</v>
+        <v>17.13813</v>
       </c>
       <c r="D2" t="n">
-        <v>16.868</v>
+        <v>16.81216</v>
       </c>
       <c r="E2" t="n">
-        <v>16.80715</v>
+        <v>17.00647</v>
       </c>
       <c r="F2" t="n">
-        <v>42.05449</v>
+        <v>41.86643</v>
       </c>
       <c r="G2" t="n">
-        <v>0.051</v>
+        <v>0.0506</v>
       </c>
       <c r="H2" t="n">
-        <v>1.88299</v>
+        <v>1.82278</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.14576</v>
+        <v>17.01736</v>
       </c>
       <c r="D3" t="n">
-        <v>17.23513</v>
+        <v>16.68322</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70171</v>
+        <v>16.9586</v>
       </c>
       <c r="F3" t="n">
-        <v>43.29904</v>
+        <v>44.1579</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05126</v>
+        <v>0.05183</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82193</v>
+        <v>1.83801</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.01</v>
+        <v>16.99328</v>
       </c>
       <c r="D4" t="n">
-        <v>16.95622</v>
+        <v>16.79837</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75284</v>
+        <v>16.91405</v>
       </c>
       <c r="F4" t="n">
-        <v>42.24634</v>
+        <v>43.27859</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05114</v>
+        <v>0.05181</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82512</v>
+        <v>1.83949</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.85701</v>
+        <v>17.26523</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10157</v>
+        <v>16.47261</v>
       </c>
       <c r="E6" t="n">
-        <v>16.86108</v>
+        <v>16.72581</v>
       </c>
       <c r="F6" t="n">
-        <v>22.24299</v>
+        <v>21.91093</v>
       </c>
       <c r="G6" t="n">
-        <v>34.94755</v>
+        <v>34.65216</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.91348</v>
+        <v>17.14029</v>
       </c>
       <c r="D7" t="n">
-        <v>16.38205</v>
+        <v>16.12329</v>
       </c>
       <c r="E7" t="n">
-        <v>16.24966</v>
+        <v>16.88362</v>
       </c>
       <c r="F7" t="n">
-        <v>22.15677</v>
+        <v>22.07373</v>
       </c>
       <c r="G7" t="n">
-        <v>34.68624</v>
+        <v>34.52703</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.6441</v>
+        <v>17.23493</v>
       </c>
       <c r="D8" t="n">
-        <v>16.39428</v>
+        <v>16.33419</v>
       </c>
       <c r="E8" t="n">
-        <v>16.37951</v>
+        <v>16.64917</v>
       </c>
       <c r="F8" t="n">
-        <v>21.96922</v>
+        <v>21.76889</v>
       </c>
       <c r="G8" t="n">
-        <v>34.54134</v>
+        <v>34.47097</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61383</v>
+        <v>0.60569</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12638</v>
+        <v>1.13002</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60044</v>
+        <v>0.61648</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13746</v>
+        <v>1.11248</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61847</v>
+        <v>0.6204</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11429</v>
+        <v>1.12874</v>
       </c>
     </row>
   </sheetData>
